--- a/docs/import-samples/ucas_exam_import_db_no_room_codes.xlsx
+++ b/docs/import-samples/ucas_exam_import_db_no_room_codes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\PTIT DOC\IST\UCAS\docs\import-samples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2B81B40-8A17-4129-9498-9B2F6B5E5775}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3F756E2-A8F0-4F22-87DB-FF597AD4901F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="1695" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="exam_import" sheetId="1" r:id="rId1"/>
@@ -1704,7 +1704,7 @@
         <v>69</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>11</v>
